--- a/tools/portal_frame_gen/templates/portal_frame_template.xlsx
+++ b/tools/portal_frame_gen/templates/portal_frame_template.xlsx
@@ -7,9 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="portal_frame" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="입력" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="span">'입력'!$F$5</definedName>
+    <definedName name="eave_height">'입력'!$F$6</definedName>
+    <definedName name="roof_pitch">'입력'!$F$7</definedName>
+    <definedName name="bays">'입력'!$F$8</definedName>
+    <definedName name="bay_spacing">'입력'!$F$9</definedName>
+    <definedName name="frame_mode">'입력'!$F$12</definedName>
+    <definedName name="material">'입력'!$F$15</definedName>
+    <definedName name="sec_column">'입력'!$F$18</definedName>
+    <definedName name="sec_rafter">'입력'!$F$19</definedName>
+    <definedName name="sec_eave_strut">'입력'!$F$20</definedName>
+    <definedName name="support">'입력'!$F$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'입력'!$A$1:$N$24</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +38,55 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +94,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -130,24 +213,59 @@
     <author>portal_frame_gen</author>
   </authors>
   <commentList>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>MIDAS 현재 모델에 이미 정의된 이름이어야 함</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>MIDAS 현재 모델에 이미 정의된 이름이어야 함</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>MIDAS 현재 모델에 이미 정의된 이름이어야 함</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>MIDAS 현재 모델에 이미 정의된 이름이어야 함</t>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>m, 기둥 중심선 간 거리</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>m, 지점 레벨에서 이브(기둥·rafter 교점)까지 수직높이. 처마 끝 아님</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>rise/run. 0.15 또는 3:12 / 3/12. 각도 아님. (0.15 = 1.5:10)</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>정수 ≥ 1</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>m, 프레임 간 거리</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>2D 또는 3D 만</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>MIDAS 재료 DB에 이미 존재해야 함. 정확히 일치</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>MIDAS 단면 DB에 이미 존재해야 함. 대소문자·공백 정확히 일치</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>MIDAS 단면 DB에 이미 존재해야 함. 대소문자·공백 정확히 일치</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>3D 전용 — 2D에서는 무시됨</t>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0" shapeId="0">
+      <text>
+        <t>pinned 또는 fixed 만</t>
       </text>
     </comment>
   </commentList>
@@ -441,161 +559,359 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="3.4" customWidth="1" min="1" max="1"/>
+    <col width="3.4" customWidth="1" min="2" max="2"/>
+    <col width="3.4" customWidth="1" min="3" max="3"/>
+    <col width="3.4" customWidth="1" min="4" max="4"/>
+    <col width="3.4" customWidth="1" min="5" max="5"/>
+    <col width="3.4" customWidth="1" min="6" max="6"/>
+    <col width="3.4" customWidth="1" min="7" max="7"/>
+    <col width="3.4" customWidth="1" min="8" max="8"/>
+    <col width="3.4" customWidth="1" min="9" max="9"/>
+    <col width="3.4" customWidth="1" min="10" max="10"/>
+    <col width="3.4" customWidth="1" min="11" max="11"/>
+    <col width="3.4" customWidth="1" min="12" max="12"/>
+    <col width="3.4" customWidth="1" min="13" max="13"/>
+    <col width="3.4" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>span_m</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>eave_height_m</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pitch_rise</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pitch_run</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>roof_angle_deg</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>bay_count</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bay_spacing_m</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>base_level_m</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>column_section</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>rafter_section</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>eave_strut_section</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>material_name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>base_fixity</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>frame_mode</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>포탈 프레임 모델 생성 입력 시트   (단위: m, kN)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>[1. 형상]</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>스팬 (m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="J5" s="8" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>처마고 (m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="J6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>지붕물매 (rise:run)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="J7" s="8" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>베이 수</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="J8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G2" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>베이 간격 (m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="J9" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>[2. 프레임 모드]</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>프레임 모드</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>[3. 재료 — MIDAS DB에 미리 정의]</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>재료명</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>SS275</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>[4. 단면 — MIDAS DB에 미리 정의]</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>기둥 단면명</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>H-400x200x8x13</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>rafter 단면명</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>H-350x175x7x11</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>이브 스트럿 단면명 (3D 전용)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>H-200x100x5.5x8</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>SS275</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>[5. 지점]</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>지점 조건</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
         <is>
           <t>pinned</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t># 단면명(column/rafter/eave_strut)과 material_name 은 MIDAS 현재 모델에 이미 정의돼 있어야 함. roof_angle_deg 를 채우면 pitch_rise/run 대신 사용. frame_mode=2D 면 bay_* 무시. base_fixity: pinned|fixed.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A1:N2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A11:N11"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A14:N14"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2D,3D"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"pinned,fixed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>